--- a/作成中事業計画書/20261001【更新版】作成中【指定様式】事業計画書（その３）第8回フォーマット.xlsx
+++ b/作成中事業計画書/20261001【更新版】作成中【指定様式】事業計画書（その３）第8回フォーマット.xlsx
@@ -3531,7 +3531,7 @@
     <t>専用パレット（1,200袋）へ開梱・ほぐし・片付け込みで約2分／枚。125枚と84枚の日の月平均</t>
   </si>
   <si>
-    <t>約2時間に1回、パレットを装置へ装填し空パレットを取り出す（約3分／回）。遅番はオペレーターが兼務</t>
+    <t>約2.5〜3時間に1回（1日4〜6回）、パレットを装填し空パレットを取り出す（約3分／回）。遅番はオペレーターが兼務</t>
   </si>
   <si>
     <t>パウチ形状が変わる品種切替時に、機内25枚のガイド幅を替える（約1.1分／枚≒28分）。月平均</t>
@@ -3548,12 +3548,12 @@
 ・労働時間削減額9,047,144円／年＝799/60×245×2,773。
 →投資回収期間＝101,200,000÷（9,047,144＋297,960,717）≒0.33年。
 ・増加した付加価値額を1年あたり（297,960,717÷3＝99,320,239円）とした場合も、101,200,000÷（9,047,144＋99,320,239）≒0.93年で、1年未満で回収できる。
-・Gライン部門のみで見た場合：キャパ不足で断っていた約4億円規模の案件に、全社の付加価値率13.66％（2026年3月期：1,525,628,095円÷11,168,904,537円）を当てはめると付加価値額は年約5,464万円となり、101,200,000÷（9,047,144＋54,640,000）≒1.59年で回収できる。</t>
+・Gライン部門のみで見た場合：1年目に受注する断った案件の約半分（約2億円）に、全社の付加価値率13.66％（2026年3月期：1,525,628,095円÷11,168,904,537円）を当てはめると付加価値額は年約2,732万円となり、101,200,000÷（9,047,144＋27,320,000）≒2.78年で、耐用年数（10年）の範囲内で回収できる。</t>
   </si>
   <si>
     <t>付加価値額（営業利益＋人件費＋減価償却費）は、基準年度（2028年3月期）1,593,327,430円→1年目1,692,179,517円→2年目1,791,169,755円→3年目（2031年3月期）1,891,288,147円（基準年度比＋297,960,717円、年平均成長率5.88％）と推移する。
-（1）売上高：パウチ自動供給装置の通年稼働で遅番の投入担当が不要になり、17.5時間稼働が安定する。キャパ不足で断っていた約4億円規模の案件（年800万袋×50円）を取り込み、1年目は前年比＋4.0％（＋460百万円）とする。2年目は日勤へ戻った社員による提案型ODMの獲得、3年目はその定着で各＋4.0％とし、売上高は11,506百万円→12,943百万円となる。年＋4.0％は清涼飲料の生産者販売金額の伸び（2025年＋5.3％）を下回る保守的な水準である。
-（2）売上原価率：省力化による労務費の抑制（別紙３の労働時間削減額9,047,144円／年）、利益率の高い提案型ODMの比率向上、価格転嫁により年0.25pt改善し、90.50％→89.75％とする。その他販管費は売上高比4.77％を維持し、営業利益は214百万円→330百万円となる。
+（1）売上高：本装置は製袋機の能力を上げないが、供給待ちによる停止（1日約30分）の解消と土曜稼働（月2日）で年約470万袋の余地が生まれる。生産能力の不足で断った案件（年800万袋×50円）の約半分（約2億円）を受注し、価格転嫁（＋1.5％）と既存顧客の増量を加えて1年目は前年比＋4.0％（＋460百万円）とする。2年目は日勤へ戻った社員による提案型ODMの獲得、3年目はその定着で各＋4.0％とし、売上高は11,506百万円→12,943百万円となる。年＋4.0％は清涼飲料の生産者販売金額の伸び（2025年＋5.3％）を下回る保守的な水準である。
+（2）売上原価率：ODM売上比率を約10％→3年目約14.5％に高め（年＋0.30pt）、価格転嫁（＋0.05pt）と労務費の抑制（1年目＋0.07pt）で賃上げによる労務費率の上昇を吸収し、保守的に年0.25pt改善して、90.50％→89.75％とする。その他販管費は売上高比4.77％を維持し、営業利益は214百万円→330百万円となる。
 （3）人件費：1人当たり年3.5％の賃上げと年3〜4名の新卒採用により、1,080百万円→1,252百万円とする（役員報酬は据え置き）。
 （4）減価償却費：既存分298,864,468円に本設備（92,000,000円・定額法10年）の9,200,000円／年を加え、308,064,468円とする。
 目標値として策定する4・5年目は、ODM比率の上昇が定着して原価率を年0.30pt改善し、付加価値額は2,008,310,651円→2,127,257,599円（年平均成長率5.95％）とする。</t>
@@ -3567,8 +3567,8 @@
   </si>
   <si>
     <t>1人当たり給与支給総額＝全月分の給与等の支給を受けた従業員の給与支給総額（給料・賞与・課税対象の手当。法定福利費・退職金は除く）÷同従業員数。直近の2026年3月期は4,319,298円（717,003,483円÷166名）である。
-2026年4月に総額約5％の賃上げを実施済みであるが、計画では保守的に、足下は年3％を上回る水準（年平均成長率3.02％）で基準年度4,584,175円（829,735,675円÷181名）とする。
-基準年度以降は年3.5％を上回る引上げを続け、1年目4,745,570円（184名）→2年目4,912,647円（188名）→3年目5,085,606円（191名、給与支給総額971,350,746円）となり、年平均成長率3.52％で必須要件（3.5％以上）を満たす。目標値として策定する4・5年目も同じ水準を続け、5年目は5,450,006円（年平均3.52％）とする。
+2026年4月に人件費総額ベースで約5％の賃上げを実施済みであるが、1人当たりの平均は新卒・中途の入替で伸びが小さくなるため、計画では保守的に、足下は年3％を上回る水準（年平均成長率3.02％）で基準年度4,584,175円（829,735,675円÷181名）とする。
+基準年度以降は既存従業員を年約4％引き上げ（新卒入社による平均の引下げ約−0.5pt）、1年目4,745,570円（184名）→2年目4,912,647円（188名）→3年目5,085,606円（191名、給与支給総額971,350,746円）となり、年平均成長率3.52％で必須要件（3.5％以上）を満たす。目標値として策定する4・5年目も同じ水準を続け、5年目は5,450,006円（年平均3.52％）とする。
 原資は安定稼働とODM比率向上による収益の拡大と労務費の抑制であり、給与支給総額の増加（基準年度比141,615,071円）を織り込んでも、営業利益は116,319,131円増加する。役員報酬は据え置き、従業員へ厚く配分する。賃上げ目標は従業員へ表明し、確実に実行する。</t>
     <phoneticPr fontId="1"/>
   </si>
